--- a/04_DESIGN_TABLES/DesignTable_4601.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_4601.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P53"/>
+  <dimension ref="A1:R53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,6 +499,16 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>DH@BORE</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3152,24 +3162,55 @@
           <t>4601-04-04-NWO-FG</t>
         </is>
       </c>
+      <c r="B45" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
           <t>4601-04-04-NWO-FG</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>7/16-20 (B UN/UNF-2A)</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4601-04-04 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4601-04-04 NWO (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4601-04-04 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4601-04-04 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); Brennan hose drill 0.189 not modelled: Q-HOSEB-BORE (a) = one bore 0.172 (D@BORE) through both legs</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3180,6 +3221,11 @@
       <c r="P45" t="inlineStr">
         <is>
           <t>4601-04-04-NWO-FG</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -3189,24 +3235,55 @@
           <t>4601-08-06-NWO-FG</t>
         </is>
       </c>
+      <c r="B46" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>4601-08-06-NWO-FG</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>9/16-18 (B UN/UNF-2A)</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4601-08-06 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4601-08-06 NWO (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4601-08-06 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4601-08-06 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); Brennan hose drill 0.406 not modelled: Q-HOSEB-BORE (a) = one bore 0.297 (D@BORE) through both legs</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -3217,6 +3294,11 @@
       <c r="P46" t="inlineStr">
         <is>
           <t>4601-08-06-NWO-FG</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -3226,24 +3308,55 @@
           <t>4601-12-10-NWO-FG</t>
         </is>
       </c>
+      <c r="B47" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
           <t>4601-12-10-NWO-FG</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>7/8-14 (B UN/UNF-2A)</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4601-12-10 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4601-12-10 NWO (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4601-12-10 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4601-12-10 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); Brennan hose drill 0.625 not modelled: Q-HOSEB-BORE (a) = one bore 0.484 (D@BORE) through both legs</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -3254,6 +3367,11 @@
       <c r="P47" t="inlineStr">
         <is>
           <t>4601-12-10-NWO-FG</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -3263,24 +3381,55 @@
           <t>4601-16-16-NWO-FG</t>
         </is>
       </c>
+      <c r="B48" t="n">
+        <v>2.394</v>
+      </c>
+      <c r="C48" t="n">
+        <v>2.039</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
           <t>4601-16-16-NWO-FG</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>1 5/16-12 (B UN/UNF-2A)</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4601-16-16 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4601-16-16 NWO (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4601-16-16 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4601-16-16 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); Brennan hose drill 0.844 not modelled: Q-HOSEB-BORE (a) = one bore 0.844 (D@BORE) through both legs</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -3291,6 +3440,11 @@
       <c r="P48" t="inlineStr">
         <is>
           <t>4601-16-16-NWO-FG</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -3300,24 +3454,55 @@
           <t>4601-16-20-NWO-FG</t>
         </is>
       </c>
+      <c r="B49" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C49" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>4601-16-20-NWO-FG</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>1 5/8-12 (B UN/UNF-2A)</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4601-16-20 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4601-16-20 NWO (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4601-16-20 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4601-16-20 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); Brennan hose drill 0.844 not modelled: Q-HOSEB-BORE (a) = one bore 1.078 (D@BORE) through both legs</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -3328,6 +3513,14 @@
       <c r="P49" t="inlineStr">
         <is>
           <t>4601-16-20-NWO-FG</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -3337,24 +3530,55 @@
           <t>4601-20-16-NWO-FG</t>
         </is>
       </c>
+      <c r="B50" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1 1/4</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
           <t>4601-20-16-NWO-FG</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>1 5/16-12 (B UN/UNF-2A)</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4601-20-16 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4601-20-16 NWO (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4601-20-16 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4601-20-16 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); Brennan hose drill 1.094 not modelled: Q-HOSEB-BORE (a) = one bore 0.844 (D@BORE) through both legs</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -3365,6 +3589,11 @@
       <c r="P50" t="inlineStr">
         <is>
           <t>4601-20-16-NWO-FG</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -3374,24 +3603,55 @@
           <t>4601-20-20-NWO-FG</t>
         </is>
       </c>
+      <c r="B51" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="C51" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1 1/4</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>4601-20-20-NWO-FG</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>1 5/8-12 (B UN/UNF-2A)</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4601-20-20 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4601-20-20 NWO (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4601-20-20 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4601-20-20 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); Brennan hose drill 1.094 not modelled: Q-HOSEB-BORE (a) = one bore 1.078 (D@BORE) through both legs</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -3402,6 +3662,11 @@
       <c r="P51" t="inlineStr">
         <is>
           <t>4601-20-20-NWO-FG</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -3411,24 +3676,55 @@
           <t>4601-24-20-NWO-FG</t>
         </is>
       </c>
+      <c r="B52" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C52" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1 1/2</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
           <t>4601-24-20-NWO-FG</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>1 5/8-12 (B UN/UNF-2A)</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4601-24-20 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4601-24-20 NWO (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4601-24-20 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4601-24-20 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); Brennan hose drill 1.343 not modelled: Q-HOSEB-BORE (a) = one bore 1.078 (D@BORE) through both legs</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -3439,6 +3735,11 @@
       <c r="P52" t="inlineStr">
         <is>
           <t>4601-24-20-NWO-FG</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -3448,24 +3749,55 @@
           <t>4601-24-24-NWO-FG</t>
         </is>
       </c>
+      <c r="B53" t="n">
+        <v>2.697</v>
+      </c>
+      <c r="C53" t="n">
+        <v>2.382</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1 1/2</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr">
         <is>
           <t>4601-24-24-NWO-FG</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1 7/8-12 (B UN/UNF-2A)</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4601-24-24 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4601-24-24 NWO (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4601-24-24 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4601-24-24 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); Brennan hose drill 1.344 not modelled: Q-HOSEB-BORE (a) = one bore 1.312 (D@BORE) through both legs</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -3476,6 +3808,11 @@
       <c r="P53" t="inlineStr">
         <is>
           <t>4601-24-24-NWO-FG</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
